--- a/2027_forecast/f_model_one_step_ahead_function_check.xlsx
+++ b/2027_forecast/f_model_one_step_ahead_function_check.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\southeast_pink_salmon_preseason\2027_forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54299703-4CAF-4F9B-BC12-287DBEEF1C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E351C54D-FE1D-4AF7-BA06-FA92D49FC89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-This is a regression using data from Jyear 1997 to 2018 only for the 2025 foreacast. </t>
+This is a regression using data from Jyear 1997 to 2020 only for the 2027 foreacast. </t>
         </r>
       </text>
     </comment>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="68">
   <si>
     <t>JYear</t>
   </si>
@@ -273,6 +273,9 @@
     <t>MAPE=</t>
   </si>
   <si>
+    <t>forecast year</t>
+  </si>
+  <si>
     <t>input data</t>
   </si>
   <si>
@@ -310,6 +313,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
   </si>
 </sst>
 </file>
@@ -899,7 +908,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -957,6 +966,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1121,7 @@
             <a:rPr lang="en-US" sz="1100" b="0" baseline="0">
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(2) The formul for the observed havest in log space should update automatically.</a:t>
+            <a:t>(2) The formula for the observed havest in log space should update automatically.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1117,7 +1129,7 @@
             <a:rPr lang="en-US" sz="1100" b="0" baseline="0">
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(3) Run a regression with ln(observed harvest) for y and CPUE for x. Only use the data up through y-6 where y is the current data year. For example, for forecast year 2025, use data from Jyear 1997 to Jyear 2018 where y would be 2024 for y-6. Place the regression summary starting in cell E32.</a:t>
+            <a:t>(3) Run a regression with ln(observed harvest) for y and CPUE for x. Only use the data up through y-6 where y is the current data year. For example, for forecast year 2027, use data from Jyear 1997 to Jyear 2020. Place the regression summary starting in cell E32.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1125,7 +1137,7 @@
             <a:rPr lang="en-US" sz="1100" b="0" baseline="0">
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(4) Update the formula in cell Y23. It should be the predicted harvest for Jyesa y-5. So, for the 2025 forecast, the predicted value is for 2019 using the regression parameters in the CPUE model from Jyear 1997 to 208.  </a:t>
+            <a:t>(4) Update the formula in cell Y23. It should be the predicted harvest for Jyear to y-5. So, for the 2027 forecast, the predicted value is for Jyear = 2021 using the regression parameters in the CPUE model from Jyear 1997 to 2020.  </a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1174,7 +1186,7 @@
             <a:rPr lang="en-US" sz="1100">
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>ead(harvest=log_data$SEAKCatch_log, variables=log_data, model = SEAKCatch_log ~CPUE, start = 1997, end = 2013, model_num = "m1")</a:t>
+            <a:t>ead(harvest=log_data$SEAKCatch_log, variables=log_data, model = SEAKCatch_log ~CPUE, start = 1997, end = 2020, model_num = "m1")</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1193,7 +1205,7 @@
             <a:rPr lang="en-US" sz="1100" baseline="0">
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> out. The start and end date should be 1997 to 2018 for the 2025 forecast for the 5-year MAPE. </a:t>
+            <a:t> out. The start and end date should be 1997 to 2020 for the 2027 forecast for the 5-year MAPE. </a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1239,7 +1251,7 @@
               <a:effectLst/>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> for the lat 5 years.</a:t>
+            <a:t> for the last 5 years.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1271,7 +1283,7 @@
               <a:effectLst/>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(harvest=log_data$SEAKCatch_log, variables=log_data, model.formulas=model.formulas,model.names=model.names, start = 1997, end = 2018)  function in the 1_summarize_models.r file with the same start and end years as in step #5 above. The output will be placed in a csv file in the results folder. The file will be called seak_model_summary_one_step_ahead5.csv.</a:t>
+            <a:t>(harvest=log_data$SEAKCatch_log, variables=log_data, model.formulas=model.formulas,model.names=model.names, start = 1997, end = 2020)  function in the 1_summarize_models.r file with the same start and end years as in step #5 above. The output will be placed in a csv file in the results folder. The file will be called seak_model_summary_one_step_ahead5.csv.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3624,7 +3636,7 @@
         <v>3.0568402608834302</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z27" s="1">
         <v>3.0445220000000002</v>
@@ -3715,7 +3727,7 @@
         <v>3.0445224377234199</v>
       </c>
       <c r="X28" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z28" t="s">
         <v>51</v>
@@ -3832,10 +3844,18 @@
       <c r="L31"/>
       <c r="M31"/>
       <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31"/>
+      <c r="O31" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="R31" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
@@ -3905,10 +3925,10 @@
         <v>1997</v>
       </c>
       <c r="P34" s="2">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="Q34" s="2">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="R34" s="2">
         <v>5</v>
@@ -3932,10 +3952,10 @@
         <v>1997</v>
       </c>
       <c r="P35" s="2">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="Q35" s="2">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="R35" s="2">
         <v>10</v>
@@ -4236,7 +4256,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
@@ -4258,24 +4278,24 @@
         <v>4.2050455869413401</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C58">
         <v>0.43302768000000003</v>
@@ -4293,13 +4313,13 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L58" s="2">
         <v>1E-3</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N58" s="2">
         <v>3.748297</v>
@@ -4307,7 +4327,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
@@ -4328,13 +4348,13 @@
         <v>2</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L59" s="2">
         <v>1E-3</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N59" s="2">
         <v>4.354374</v>
@@ -4345,13 +4365,13 @@
         <v>3</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L60" s="2">
         <v>1E-3</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N60" s="2">
         <v>3.0081039999999999</v>
@@ -4362,13 +4382,13 @@
         <v>4</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L61" s="2">
         <v>1E-3</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N61" s="2">
         <v>4.2050460000000003</v>
@@ -4379,13 +4399,13 @@
         <v>5</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L62" s="2">
         <v>1E-3</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N62" s="2">
         <v>3.813647</v>
@@ -4396,13 +4416,13 @@
         <v>6</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L63" s="2">
         <v>1E-3</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N63" s="2">
         <v>3.9601790000000001</v>
@@ -4413,13 +4433,13 @@
         <v>7</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L64" s="2">
         <v>1E-3</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N64" s="2">
         <v>3.8135219999999999</v>
@@ -4430,13 +4450,13 @@
         <v>8</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L65" s="2">
         <v>1E-3</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N65" s="2">
         <v>4.0795940000000002</v>
@@ -4447,13 +4467,13 @@
         <v>9</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L66" s="2">
         <v>1E-3</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N66" s="2">
         <v>2.451565</v>
@@ -4464,13 +4484,13 @@
         <v>10</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L67" s="2">
         <v>1E-3</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N67" s="2">
         <v>3.8021280000000002</v>
@@ -4478,19 +4498,19 @@
     </row>
     <row r="68" spans="8:14" x14ac:dyDescent="0.3">
       <c r="H68" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J68" s="2">
         <v>11</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L68" s="2">
         <v>1E-3</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N68" s="2">
         <v>2.76688</v>
@@ -4501,13 +4521,13 @@
         <v>12</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L69" s="2">
         <v>1E-3</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N69" s="2">
         <v>4.0755359999999996</v>
@@ -4518,13 +4538,13 @@
         <v>13</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L70" s="2">
         <v>1E-3</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N70" s="2">
         <v>3.0576279999999998</v>
@@ -4535,13 +4555,13 @@
         <v>14</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L71" s="2">
         <v>1E-3</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N71" s="2">
         <v>4.5509190000000004</v>
@@ -4552,13 +4572,13 @@
         <v>15</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L72" s="2">
         <v>1E-3</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N72" s="2">
         <v>3.6156060000000001</v>
@@ -4569,13 +4589,13 @@
         <v>16</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L73" s="2">
         <v>1E-3</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N73" s="2">
         <v>3.5579890000000001</v>
@@ -4586,13 +4606,13 @@
         <v>17</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L74" s="2">
         <v>1E-3</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N74" s="2">
         <v>2.9109479999999999</v>
@@ -4603,13 +4623,13 @@
         <v>18</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L75" s="2">
         <v>1E-3</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N75" s="2">
         <v>3.5477409999999998</v>
@@ -4620,13 +4640,13 @@
         <v>19</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L76" s="2">
         <v>1E-3</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N76" s="2">
         <v>2.0878679999999998</v>
@@ -4637,13 +4657,13 @@
         <v>20</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L77" s="2">
         <v>1E-3</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N77" s="2">
         <v>3.0512570000000001</v>
@@ -4654,13 +4674,13 @@
         <v>21</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L78" s="2">
         <v>1E-3</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N78" s="2">
         <v>2.0872839999999999</v>
@@ -4671,13 +4691,13 @@
         <v>22</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L79" s="2">
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N79" s="2">
         <v>3.882145</v>
@@ -4688,13 +4708,13 @@
         <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L80" s="2">
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N80" s="2">
         <v>2.9068550000000002</v>
@@ -4705,13 +4725,13 @@
         <v>24</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L81" s="2">
         <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N81" s="2">
         <v>3.8806150000000001</v>
@@ -4722,13 +4742,13 @@
         <v>25</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L82" s="2">
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N82" s="2">
         <v>3.0016069999999999</v>
@@ -4739,13 +4759,13 @@
         <v>26</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L83" s="2">
         <v>1</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N83" s="2">
         <v>3.0568399999999998</v>
@@ -4756,13 +4776,13 @@
         <v>27</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L84" s="2">
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N84" s="2">
         <v>3.0445220000000002</v>
@@ -4773,16 +4793,16 @@
         <v>28</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L85" s="2">
         <v>1</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
